--- a/Excel_jumia_dataset -CLEANED.xlsx
+++ b/Excel_jumia_dataset -CLEANED.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Documents\Data Science and AI(LUX)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Documents\GitHub\JUMIA-DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B8F548-263C-44B2-9508-BAB625C6A76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4490A1DF-48E3-414C-93E3-62E1C82A67C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="10" xr2:uid="{2D74EB56-4582-4F0D-BB92-CD4FA1141519}"/>
   </bookViews>
@@ -48,15 +48,15 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="61" r:id="rId15"/>
-    <pivotCache cacheId="59" r:id="rId16"/>
-    <pivotCache cacheId="57" r:id="rId17"/>
-    <pivotCache cacheId="58" r:id="rId18"/>
-    <pivotCache cacheId="20" r:id="rId19"/>
-    <pivotCache cacheId="40" r:id="rId20"/>
-    <pivotCache cacheId="44" r:id="rId21"/>
-    <pivotCache cacheId="62" r:id="rId22"/>
-    <pivotCache cacheId="63" r:id="rId23"/>
+    <pivotCache cacheId="0" r:id="rId15"/>
+    <pivotCache cacheId="1" r:id="rId16"/>
+    <pivotCache cacheId="2" r:id="rId17"/>
+    <pivotCache cacheId="3" r:id="rId18"/>
+    <pivotCache cacheId="4" r:id="rId19"/>
+    <pivotCache cacheId="5" r:id="rId20"/>
+    <pivotCache cacheId="6" r:id="rId21"/>
+    <pivotCache cacheId="7" r:id="rId22"/>
+    <pivotCache cacheId="8" r:id="rId23"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -980,7 +980,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -999,7 +999,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -11317,49 +11316,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -12549,6 +12506,48 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -12592,6 +12591,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-10DB-40F3-AE3C-B824FE236256}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -12607,6 +12611,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-10DB-40F3-AE3C-B824FE236256}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -12622,6 +12631,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-10DB-40F3-AE3C-B824FE236256}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -12912,6 +12926,48 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -12945,6 +13001,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-856E-4E42-9B40-E8608D64563F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -12960,6 +13021,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-856E-4E42-9B40-E8608D64563F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -12975,6 +13041,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-856E-4E42-9B40-E8608D64563F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -27667,8 +27738,8 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Discount2 2">
@@ -27691,7 +27762,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -27786,8 +27857,8 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Product 2">
@@ -27810,7 +27881,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -27905,8 +27976,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>22225</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Product">
@@ -27929,7 +28000,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -27983,8 +28054,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>3175</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Discount2">
@@ -28007,7 +28078,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28061,8 +28132,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>149225</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Ratingd">
@@ -28085,7 +28156,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28180,8 +28251,8 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="discount">
@@ -28204,7 +28275,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28335,8 +28406,8 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>136525</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Ratingd 2">
@@ -28359,7 +28430,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28454,8 +28525,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>60325</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="Product 3">
@@ -28478,7 +28549,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28532,8 +28603,8 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="product category 1">
@@ -28556,7 +28627,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28651,8 +28722,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Product 4">
@@ -28675,7 +28746,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28729,8 +28800,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="product category 2">
@@ -28753,7 +28824,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28848,8 +28919,8 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>73025</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Ratingd 1">
@@ -28872,7 +28943,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28926,8 +28997,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>3175</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="discounts category">
@@ -28950,7 +29021,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -29045,8 +29116,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Review">
@@ -29069,7 +29140,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -29123,8 +29194,8 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="discounts category 1">
@@ -29147,7 +29218,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -29403,7 +29474,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Total products  = 115</a:t>
           </a:r>
         </a:p>
@@ -29464,7 +29535,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Average rating = 3.9</a:t>
           </a:r>
         </a:p>
@@ -29525,7 +29596,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Average discount percentage = 37%</a:t>
           </a:r>
         </a:p>
@@ -29586,7 +29657,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Total reviews = 723</a:t>
           </a:r>
         </a:p>
@@ -29647,7 +29718,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Average current price=1174.36</a:t>
           </a:r>
         </a:p>
@@ -29708,7 +29779,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Average old price=1797.07</a:t>
           </a:r>
         </a:p>
@@ -29843,8 +29914,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>89960</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="22" name="Product 1">
@@ -29867,7 +29938,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -29959,8 +30030,8 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>134056</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="24" name="Discount2 3">
@@ -29983,7 +30054,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -30075,8 +30146,8 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>141112</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="26" name="Ratingd 3">
@@ -30099,7 +30170,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -30381,8 +30452,8 @@
       <xdr:row>60</xdr:row>
       <xdr:rowOff>176389</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="38" name="discount 1">
@@ -30405,7 +30476,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -37095,7 +37166,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1989D91C-64AD-4917-9A9F-6EE635C047DD}" name="PivotTable2" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1989D91C-64AD-4917-9A9F-6EE635C047DD}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:B51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -37412,7 +37483,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B82A1C2-CEC1-4E74-AEAE-BC0839751136}" name="PivotTable9" cacheId="57" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B82A1C2-CEC1-4E74-AEAE-BC0839751136}" name="PivotTable9" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -37550,7 +37621,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F41ECC8C-E275-49C9-8825-F24CA3DBE203}" name="PivotTable10" cacheId="58" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F41ECC8C-E275-49C9-8825-F24CA3DBE203}" name="PivotTable10" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -37677,7 +37748,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{72FABC8B-A4EE-4708-8ED6-D31A9EE495B2}" name="PivotTable3" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{72FABC8B-A4EE-4708-8ED6-D31A9EE495B2}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A3:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -37891,7 +37962,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0CB93205-8C01-4798-84CD-54712881425F}" name="PivotTable3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0CB93205-8C01-4798-84CD-54712881425F}" name="PivotTable3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0">
@@ -38127,7 +38198,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9C76E81-BE8D-4AF7-9FD0-81B52F5CB37F}" name="PivotTable5" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9C76E81-BE8D-4AF7-9FD0-81B52F5CB37F}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField dataField="1" showAll="0">
@@ -38441,7 +38512,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6D8528C-4E38-43A6-85E6-8CF77B81AE59}" name="PivotTable11" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6D8528C-4E38-43A6-85E6-8CF77B81AE59}" name="PivotTable11" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -38715,7 +38786,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B686F092-BAB1-4988-B540-3D5B3C25B010}" name="PivotTable12" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B686F092-BAB1-4988-B540-3D5B3C25B010}" name="PivotTable12" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -38822,7 +38893,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F6E1140-D151-4F4D-9437-608679FFA07C}" name="PivotTable9" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F6E1140-D151-4F4D-9437-608679FFA07C}" name="PivotTable9" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -38922,7 +38993,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{950B7C69-5DFF-4B66-9957-802024B6C30A}" name="PivotTable10" cacheId="44" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{950B7C69-5DFF-4B66-9957-802024B6C30A}" name="PivotTable10" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -39033,7 +39104,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4881467F-6248-41F0-A110-854F58D0FE73}" name="PivotTable7" cacheId="59" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4881467F-6248-41F0-A110-854F58D0FE73}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A1:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -40157,37 +40228,32 @@
       <c r="A4" s="11">
         <v>0.01</v>
       </c>
-      <c r="B4" s="14"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>0.02</v>
       </c>
-      <c r="B5" s="14"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>0.03</v>
       </c>
-      <c r="B6" s="14"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>0.04</v>
       </c>
-      <c r="B7" s="14"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>0.08</v>
       </c>
-      <c r="B8" s="14"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>0.09</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9">
         <v>15</v>
       </c>
     </row>
@@ -40195,13 +40261,12 @@
       <c r="A10" s="11">
         <v>0.11</v>
       </c>
-      <c r="B10" s="14"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>0.13</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11">
         <v>6</v>
       </c>
     </row>
@@ -40209,13 +40274,12 @@
       <c r="A12" s="11">
         <v>0.14000000000000001</v>
       </c>
-      <c r="B12" s="14"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>0.18</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13">
         <v>12</v>
       </c>
     </row>
@@ -40223,7 +40287,7 @@
       <c r="A14" s="11">
         <v>0.19</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14">
         <v>5</v>
       </c>
     </row>
@@ -40231,7 +40295,7 @@
       <c r="A15" s="11">
         <v>0.2</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15">
         <v>12</v>
       </c>
     </row>
@@ -40239,7 +40303,7 @@
       <c r="A16" s="11">
         <v>0.21</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16">
         <v>1</v>
       </c>
     </row>
@@ -40247,7 +40311,7 @@
       <c r="A17" s="11">
         <v>0.22</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17">
         <v>16</v>
       </c>
     </row>
@@ -40255,7 +40319,7 @@
       <c r="A18" s="11">
         <v>0.23</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18">
         <v>14</v>
       </c>
     </row>
@@ -40263,7 +40327,7 @@
       <c r="A19" s="11">
         <v>0.24</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19">
         <v>55</v>
       </c>
     </row>
@@ -40271,7 +40335,7 @@
       <c r="A20" s="11">
         <v>0.25</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20">
         <v>24</v>
       </c>
     </row>
@@ -40279,7 +40343,7 @@
       <c r="A21" s="11">
         <v>0.26</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21">
         <v>5</v>
       </c>
     </row>
@@ -40287,7 +40351,7 @@
       <c r="A22" s="11">
         <v>0.27</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22">
         <v>52</v>
       </c>
     </row>
@@ -40295,7 +40359,7 @@
       <c r="A23" s="11">
         <v>0.28999999999999998</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23">
         <v>5</v>
       </c>
     </row>
@@ -40303,7 +40367,7 @@
       <c r="A24" s="11">
         <v>0.3</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24">
         <v>20</v>
       </c>
     </row>
@@ -40311,7 +40375,7 @@
       <c r="A25" s="11">
         <v>0.32</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25">
         <v>13</v>
       </c>
     </row>
@@ -40319,7 +40383,7 @@
       <c r="A26" s="11">
         <v>0.33</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26">
         <v>9</v>
       </c>
     </row>
@@ -40327,7 +40391,7 @@
       <c r="A27" s="11">
         <v>0.34</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27">
         <v>51</v>
       </c>
     </row>
@@ -40335,7 +40399,7 @@
       <c r="A28" s="11">
         <v>0.35</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28">
         <v>55</v>
       </c>
     </row>
@@ -40343,19 +40407,17 @@
       <c r="A29" s="11">
         <v>0.36</v>
       </c>
-      <c r="B29" s="14"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="11">
         <v>0.36956521739130432</v>
       </c>
-      <c r="B30" s="14"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="11">
         <v>0.37</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31">
         <v>9</v>
       </c>
     </row>
@@ -40363,7 +40425,7 @@
       <c r="A32" s="11">
         <v>0.38</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B32">
         <v>4</v>
       </c>
     </row>
@@ -40371,7 +40433,7 @@
       <c r="A33" s="11">
         <v>0.39</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B33">
         <v>5</v>
       </c>
     </row>
@@ -40379,7 +40441,7 @@
       <c r="A34" s="11">
         <v>0.4</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B34">
         <v>1</v>
       </c>
     </row>
@@ -40387,7 +40449,7 @@
       <c r="A35" s="11">
         <v>0.41</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B35">
         <v>36</v>
       </c>
     </row>
@@ -40395,7 +40457,7 @@
       <c r="A36" s="11">
         <v>0.42</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36">
         <v>6</v>
       </c>
     </row>
@@ -40403,7 +40465,7 @@
       <c r="A37" s="11">
         <v>0.43</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B37">
         <v>11</v>
       </c>
     </row>
@@ -40411,7 +40473,7 @@
       <c r="A38" s="11">
         <v>0.45</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B38">
         <v>28</v>
       </c>
     </row>
@@ -40419,7 +40481,7 @@
       <c r="A39" s="11">
         <v>0.46</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39">
         <v>3</v>
       </c>
     </row>
@@ -40427,7 +40489,7 @@
       <c r="A40" s="11">
         <v>0.47</v>
       </c>
-      <c r="B40" s="14">
+      <c r="B40">
         <v>39</v>
       </c>
     </row>
@@ -40435,7 +40497,7 @@
       <c r="A41" s="11">
         <v>0.48</v>
       </c>
-      <c r="B41" s="14">
+      <c r="B41">
         <v>9</v>
       </c>
     </row>
@@ -40443,7 +40505,7 @@
       <c r="A42" s="11">
         <v>0.49</v>
       </c>
-      <c r="B42" s="14">
+      <c r="B42">
         <v>118</v>
       </c>
     </row>
@@ -40451,7 +40513,7 @@
       <c r="A43" s="11">
         <v>0.5</v>
       </c>
-      <c r="B43" s="14">
+      <c r="B43">
         <v>8</v>
       </c>
     </row>
@@ -40459,7 +40521,7 @@
       <c r="A44" s="11">
         <v>0.51</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44">
         <v>2</v>
       </c>
     </row>
@@ -40467,7 +40529,7 @@
       <c r="A45" s="11">
         <v>0.52</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45">
         <v>24</v>
       </c>
     </row>
@@ -40475,7 +40537,7 @@
       <c r="A46" s="11">
         <v>0.53</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46">
         <v>15</v>
       </c>
     </row>
@@ -40483,7 +40545,7 @@
       <c r="A47" s="11">
         <v>0.54</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47">
         <v>17</v>
       </c>
     </row>
@@ -40491,7 +40553,7 @@
       <c r="A48" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48">
         <v>18</v>
       </c>
     </row>
@@ -40499,19 +40561,17 @@
       <c r="A49" s="11">
         <v>0.61</v>
       </c>
-      <c r="B49" s="14"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="11">
         <v>0.64</v>
       </c>
-      <c r="B50" s="14"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51">
         <v>723</v>
       </c>
     </row>
@@ -41355,7 +41415,7 @@
       <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -41363,7 +41423,7 @@
       <c r="A5" s="12">
         <v>2.1</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5">
         <v>20</v>
       </c>
     </row>
@@ -41371,7 +41431,7 @@
       <c r="A6" s="12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6">
         <v>12</v>
       </c>
     </row>
@@ -41379,7 +41439,7 @@
       <c r="A7" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7">
         <v>13</v>
       </c>
     </row>
@@ -41387,7 +41447,7 @@
       <c r="A8" s="12">
         <v>2.5</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8">
         <v>6</v>
       </c>
     </row>
@@ -41395,7 +41455,7 @@
       <c r="A9" s="12">
         <v>2.6</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9">
         <v>17</v>
       </c>
     </row>
@@ -41403,7 +41463,7 @@
       <c r="A10" s="12">
         <v>2.7</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10">
         <v>15</v>
       </c>
     </row>
@@ -41411,7 +41471,7 @@
       <c r="A11" s="12">
         <v>2.8</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11">
         <v>69</v>
       </c>
     </row>
@@ -41419,7 +41479,7 @@
       <c r="A12" s="12">
         <v>2.9</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12">
         <v>16</v>
       </c>
     </row>
@@ -41427,7 +41487,7 @@
       <c r="A13" s="12">
         <v>3</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13">
         <v>26</v>
       </c>
     </row>
@@ -41435,7 +41495,7 @@
       <c r="A14" s="12">
         <v>3.3</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14">
         <v>13</v>
       </c>
     </row>
@@ -41443,7 +41503,7 @@
       <c r="A15" s="12">
         <v>3.8</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15">
         <v>30</v>
       </c>
     </row>
@@ -41451,7 +41511,7 @@
       <c r="A16" s="12">
         <v>4</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16">
         <v>24</v>
       </c>
     </row>
@@ -41459,7 +41519,7 @@
       <c r="A17" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17">
         <v>46</v>
       </c>
     </row>
@@ -41467,7 +41527,7 @@
       <c r="A18" s="12">
         <v>4.2</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18">
         <v>9</v>
       </c>
     </row>
@@ -41475,7 +41535,7 @@
       <c r="A19" s="12">
         <v>4.3</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19">
         <v>61</v>
       </c>
     </row>
@@ -41483,7 +41543,7 @@
       <c r="A20" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20">
         <v>14</v>
       </c>
     </row>
@@ -41491,7 +41551,7 @@
       <c r="A21" s="12">
         <v>4.5</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21">
         <v>42</v>
       </c>
     </row>
@@ -41499,7 +41559,7 @@
       <c r="A22" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22">
         <v>177</v>
       </c>
     </row>
@@ -41507,7 +41567,7 @@
       <c r="A23" s="12">
         <v>4.7</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23">
         <v>78</v>
       </c>
     </row>
@@ -41515,7 +41575,7 @@
       <c r="A24" s="12">
         <v>4.8</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24">
         <v>22</v>
       </c>
     </row>
@@ -41523,7 +41583,7 @@
       <c r="A25" s="12">
         <v>5</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25">
         <v>12</v>
       </c>
     </row>
@@ -41531,7 +41591,7 @@
       <c r="A26" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26">
         <v>723</v>
       </c>
     </row>
@@ -41573,7 +41633,7 @@
       <c r="A4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4">
         <v>25</v>
       </c>
     </row>
@@ -41581,7 +41641,7 @@
       <c r="A5" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5">
         <v>20</v>
       </c>
     </row>
@@ -41589,7 +41649,7 @@
       <c r="A6" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6">
         <v>70</v>
       </c>
     </row>
@@ -41597,7 +41657,7 @@
       <c r="A7" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7">
         <v>115</v>
       </c>
     </row>
@@ -41635,7 +41695,7 @@
       <c r="A4" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4">
         <v>30</v>
       </c>
     </row>
@@ -41643,7 +41703,7 @@
       <c r="A5" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5">
         <v>4</v>
       </c>
     </row>
@@ -41651,7 +41711,7 @@
       <c r="A6" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6">
         <v>23</v>
       </c>
     </row>
@@ -41659,7 +41719,7 @@
       <c r="A7" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7">
         <v>57</v>
       </c>
     </row>
@@ -41700,7 +41760,7 @@
       <c r="A4" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4">
         <v>3.613333333333332</v>
       </c>
     </row>
@@ -41708,7 +41768,7 @@
       <c r="A5" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5">
         <v>3.7249999999999996</v>
       </c>
     </row>
@@ -41716,7 +41776,7 @@
       <c r="A6" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6">
         <v>4.2530303030303029</v>
       </c>
     </row>
@@ -41724,7 +41784,7 @@
       <c r="A7" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7">
         <v>3.885736677115986</v>
       </c>
     </row>
@@ -41762,7 +41822,7 @@
       <c r="A4" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4">
         <v>334</v>
       </c>
     </row>
@@ -41770,7 +41830,7 @@
       <c r="A5" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5">
         <v>38</v>
       </c>
     </row>
@@ -41778,7 +41838,7 @@
       <c r="A6" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6">
         <v>351</v>
       </c>
     </row>
@@ -41786,7 +41846,7 @@
       <c r="A7" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7">
         <v>723</v>
       </c>
     </row>
@@ -41858,7 +41918,7 @@
         <v>3971</v>
       </c>
       <c r="D2" s="4">
-        <f>C2-B2</f>
+        <f t="shared" ref="D2:D33" si="0">C2-B2</f>
         <v>1946</v>
       </c>
       <c r="E2" s="1">
@@ -41871,7 +41931,7 @@
         <v>5</v>
       </c>
       <c r="H2" t="str">
-        <f>IF(G2&lt;3,"poor",IF(G2&lt;=4.5,"average",IF(G2&gt;=4.5,"excellent","")))</f>
+        <f t="shared" ref="H2:H22" si="1">IF(G2&lt;3,"poor",IF(G2&lt;=4.5,"average",IF(G2&gt;=4.5,"excellent","")))</f>
         <v>excellent</v>
       </c>
       <c r="I2" t="str">
@@ -41890,7 +41950,7 @@
         <v>2690</v>
       </c>
       <c r="D3" s="4">
-        <f>C3-B3</f>
+        <f t="shared" si="0"/>
         <v>1070</v>
       </c>
       <c r="E3" s="1">
@@ -41903,11 +41963,11 @@
         <v>5</v>
       </c>
       <c r="H3" t="str">
-        <f>IF(G3&lt;3,"poor",IF(G3&lt;=4.5,"average",IF(G3&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I64" si="0">IF(E3&lt;20%,"lowdiscount",IF(E3&lt;41%,"medium discount",IF(E3&gt;=41%,"high discount","cant rate")))</f>
+        <f t="shared" ref="I3:I64" si="2">IF(E3&lt;20%,"lowdiscount",IF(E3&lt;41%,"medium discount",IF(E3&gt;=41%,"high discount","cant rate")))</f>
         <v>medium discount</v>
       </c>
       <c r="K3" s="4"/>
@@ -41923,7 +41983,7 @@
         <v>4588</v>
       </c>
       <c r="D4" s="4">
-        <f>C4-B4</f>
+        <f t="shared" si="0"/>
         <v>948</v>
       </c>
       <c r="E4" s="1">
@@ -41936,11 +41996,11 @@
         <v>5</v>
       </c>
       <c r="H4" t="str">
-        <f>IF(G4&lt;3,"poor",IF(G4&lt;=4.5,"average",IF(G4&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -41955,7 +42015,7 @@
         <v>1920</v>
       </c>
       <c r="D5" s="4">
-        <f>C5-B5</f>
+        <f t="shared" si="0"/>
         <v>941</v>
       </c>
       <c r="E5" s="1">
@@ -41968,11 +42028,11 @@
         <v>5</v>
       </c>
       <c r="H5" t="str">
-        <f>IF(G5&lt;3,"poor",IF(G5&lt;=4.5,"average",IF(G5&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -41987,7 +42047,7 @@
         <v>684</v>
       </c>
       <c r="D6" s="4">
-        <f>C6-B6</f>
+        <f t="shared" si="0"/>
         <v>352</v>
       </c>
       <c r="E6" s="1">
@@ -42000,11 +42060,11 @@
         <v>5</v>
       </c>
       <c r="H6" t="str">
-        <f>IF(G6&lt;3,"poor",IF(G6&lt;=4.5,"average",IF(G6&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42019,7 +42079,7 @@
         <v>360</v>
       </c>
       <c r="D7" s="4">
-        <f>C7-B7</f>
+        <f t="shared" si="0"/>
         <v>189</v>
       </c>
       <c r="E7" s="1">
@@ -42032,11 +42092,11 @@
         <v>5</v>
       </c>
       <c r="H7" t="str">
-        <f>IF(G7&lt;3,"poor",IF(G7&lt;=4.5,"average",IF(G7&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42051,7 +42111,7 @@
         <v>360</v>
       </c>
       <c r="D8" s="4">
-        <f>C8-B8</f>
+        <f t="shared" si="0"/>
         <v>165</v>
       </c>
       <c r="E8" s="1">
@@ -42064,11 +42124,11 @@
         <v>5</v>
       </c>
       <c r="H8" t="str">
-        <f>IF(G8&lt;3,"poor",IF(G8&lt;=4.5,"average",IF(G8&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42083,7 +42143,7 @@
         <v>2800</v>
       </c>
       <c r="D9" s="4">
-        <f>C9-B9</f>
+        <f t="shared" si="0"/>
         <v>1526</v>
       </c>
       <c r="E9" s="1">
@@ -42096,11 +42156,11 @@
         <v>4.8</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(G9&lt;3,"poor",IF(G9&lt;=4.5,"average",IF(G9&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42115,7 +42175,7 @@
         <v>2356</v>
       </c>
       <c r="D10" s="4">
-        <f>C10-B10</f>
+        <f t="shared" si="0"/>
         <v>616</v>
       </c>
       <c r="E10" s="1">
@@ -42128,11 +42188,11 @@
         <v>4.8</v>
       </c>
       <c r="H10" t="str">
-        <f>IF(G10&lt;3,"poor",IF(G10&lt;=4.5,"average",IF(G10&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42147,7 +42207,7 @@
         <v>1035</v>
       </c>
       <c r="D11" s="4">
-        <f>C11-B11</f>
+        <f t="shared" si="0"/>
         <v>483</v>
       </c>
       <c r="E11" s="1">
@@ -42160,11 +42220,11 @@
         <v>4.8</v>
       </c>
       <c r="H11" t="str">
-        <f>IF(G11&lt;3,"poor",IF(G11&lt;=4.5,"average",IF(G11&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42179,7 +42239,7 @@
         <v>2499</v>
       </c>
       <c r="D12" s="4">
-        <f>C12-B12</f>
+        <f t="shared" si="0"/>
         <v>919</v>
       </c>
       <c r="E12" s="1">
@@ -42192,11 +42252,11 @@
         <v>4.7</v>
       </c>
       <c r="H12" t="str">
-        <f>IF(G12&lt;3,"poor",IF(G12&lt;=4.5,"average",IF(G12&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42211,7 +42271,7 @@
         <v>2650</v>
       </c>
       <c r="D13" s="4">
-        <f>C13-B13</f>
+        <f t="shared" si="0"/>
         <v>710</v>
       </c>
       <c r="E13" s="1">
@@ -42224,11 +42284,11 @@
         <v>4.7</v>
       </c>
       <c r="H13" t="str">
-        <f>IF(G13&lt;3,"poor",IF(G13&lt;=4.5,"average",IF(G13&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42243,7 +42303,7 @@
         <v>1500</v>
       </c>
       <c r="D14" s="4">
-        <f>C14-B14</f>
+        <f t="shared" si="0"/>
         <v>510</v>
       </c>
       <c r="E14" s="1">
@@ -42256,11 +42316,11 @@
         <v>4.7</v>
       </c>
       <c r="H14" t="str">
-        <f>IF(G14&lt;3,"poor",IF(G14&lt;=4.5,"average",IF(G14&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42275,7 +42335,7 @@
         <v>1490</v>
       </c>
       <c r="D15" s="4">
-        <f>C15-B15</f>
+        <f t="shared" si="0"/>
         <v>510</v>
       </c>
       <c r="E15" s="1">
@@ -42288,11 +42348,11 @@
         <v>4.7</v>
       </c>
       <c r="H15" t="str">
-        <f>IF(G15&lt;3,"poor",IF(G15&lt;=4.5,"average",IF(G15&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42307,7 +42367,7 @@
         <v>1966</v>
       </c>
       <c r="D16" s="4">
-        <f>C16-B16</f>
+        <f t="shared" si="0"/>
         <v>968</v>
       </c>
       <c r="E16" s="1">
@@ -42320,11 +42380,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H16" t="str">
-        <f>IF(G16&lt;3,"poor",IF(G16&lt;=4.5,"average",IF(G16&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42339,7 +42399,7 @@
         <v>2923</v>
       </c>
       <c r="D17" s="4">
-        <f>C17-B17</f>
+        <f t="shared" si="0"/>
         <v>724</v>
       </c>
       <c r="E17" s="1">
@@ -42352,11 +42412,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H17" t="str">
-        <f>IF(G17&lt;3,"poor",IF(G17&lt;=4.5,"average",IF(G17&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42371,7 +42431,7 @@
         <v>3032</v>
       </c>
       <c r="D18" s="4">
-        <f>C18-B18</f>
+        <f t="shared" si="0"/>
         <v>713</v>
       </c>
       <c r="E18" s="1">
@@ -42384,11 +42444,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H18" t="str">
-        <f>IF(G18&lt;3,"poor",IF(G18&lt;=4.5,"average",IF(G18&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42403,7 +42463,7 @@
         <v>3699</v>
       </c>
       <c r="D19" s="4">
-        <f>C19-B19</f>
+        <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="E19" s="1">
@@ -42416,11 +42476,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H19" t="str">
-        <f>IF(G19&lt;3,"poor",IF(G19&lt;=4.5,"average",IF(G19&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -42435,7 +42495,7 @@
         <v>647</v>
       </c>
       <c r="D20" s="4">
-        <f>C20-B20</f>
+        <f t="shared" si="0"/>
         <v>227</v>
       </c>
       <c r="E20" s="1">
@@ -42448,11 +42508,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H20" t="str">
-        <f>IF(G20&lt;3,"poor",IF(G20&lt;=4.5,"average",IF(G20&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>excellent</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42467,7 +42527,7 @@
         <v>2700</v>
       </c>
       <c r="D21" s="4">
-        <f>C21-B21</f>
+        <f t="shared" si="0"/>
         <v>900</v>
       </c>
       <c r="E21" s="1">
@@ -42480,11 +42540,11 @@
         <v>4.5</v>
       </c>
       <c r="H21" t="str">
-        <f>IF(G21&lt;3,"poor",IF(G21&lt;=4.5,"average",IF(G21&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>average</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42499,7 +42559,7 @@
         <v>2699</v>
       </c>
       <c r="D22" s="4">
-        <f>C22-B22</f>
+        <f t="shared" si="0"/>
         <v>719</v>
       </c>
       <c r="E22" s="1">
@@ -42512,11 +42572,11 @@
         <v>4.5</v>
       </c>
       <c r="H22" t="str">
-        <f>IF(G22&lt;3,"poor",IF(G22&lt;=4.5,"average",IF(G22&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="1"/>
         <v>average</v>
       </c>
       <c r="I22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42531,7 +42591,7 @@
         <v>1525</v>
       </c>
       <c r="D23" s="4">
-        <f>C23-B23</f>
+        <f t="shared" si="0"/>
         <v>575</v>
       </c>
       <c r="E23" s="1">
@@ -42548,7 +42608,7 @@
         <v>excellent</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42563,7 +42623,7 @@
         <v>860</v>
       </c>
       <c r="D24" s="4">
-        <f>C24-B24</f>
+        <f t="shared" si="0"/>
         <v>359</v>
       </c>
       <c r="E24" s="1">
@@ -42576,11 +42636,11 @@
         <v>4.5</v>
       </c>
       <c r="H24" t="str">
-        <f>IF(G24&lt;3,"poor",IF(G24&lt;=4.5,"average",IF(G24&gt;=4.5,"excellent","")))</f>
+        <f t="shared" ref="H24:H55" si="3">IF(G24&lt;3,"poor",IF(G24&lt;=4.5,"average",IF(G24&gt;=4.5,"excellent","")))</f>
         <v>average</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42595,7 +42655,7 @@
         <v>2150</v>
       </c>
       <c r="D25" s="4">
-        <f>C25-B25</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="E25" s="1">
@@ -42608,11 +42668,11 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H25" t="str">
-        <f>IF(G25&lt;3,"poor",IF(G25&lt;=4.5,"average",IF(G25&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42627,7 +42687,7 @@
         <v>4500</v>
       </c>
       <c r="D26" s="4">
-        <f>C26-B26</f>
+        <f t="shared" si="0"/>
         <v>2452</v>
       </c>
       <c r="E26" s="1">
@@ -42640,11 +42700,11 @@
         <v>4.3</v>
       </c>
       <c r="H26" t="str">
-        <f>IF(G26&lt;3,"poor",IF(G26&lt;=4.5,"average",IF(G26&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42659,7 +42719,7 @@
         <v>3490</v>
       </c>
       <c r="D27" s="4">
-        <f>C27-B27</f>
+        <f t="shared" si="0"/>
         <v>1670</v>
       </c>
       <c r="E27" s="1">
@@ -42672,11 +42732,11 @@
         <v>4.3</v>
       </c>
       <c r="H27" t="str">
-        <f>IF(G27&lt;3,"poor",IF(G27&lt;=4.5,"average",IF(G27&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42691,7 +42751,7 @@
         <v>656</v>
       </c>
       <c r="D28" s="4">
-        <f>C28-B28</f>
+        <f t="shared" si="0"/>
         <v>267</v>
       </c>
       <c r="E28" s="1">
@@ -42704,11 +42764,11 @@
         <v>4.3</v>
       </c>
       <c r="H28" t="str">
-        <f>IF(G28&lt;3,"poor",IF(G28&lt;=4.5,"average",IF(G28&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42723,7 +42783,7 @@
         <v>382</v>
       </c>
       <c r="D29" s="4">
-        <f>C29-B29</f>
+        <f t="shared" si="0"/>
         <v>197</v>
       </c>
       <c r="E29" s="1">
@@ -42736,11 +42796,11 @@
         <v>4.3</v>
       </c>
       <c r="H29" t="str">
-        <f>IF(G29&lt;3,"poor",IF(G29&lt;=4.5,"average",IF(G29&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42755,7 +42815,7 @@
         <v>2499</v>
       </c>
       <c r="D30" s="4">
-        <f>C30-B30</f>
+        <f t="shared" si="0"/>
         <v>819</v>
       </c>
       <c r="E30" s="1">
@@ -42768,11 +42828,11 @@
         <v>4.2</v>
       </c>
       <c r="H30" t="str">
-        <f>IF(G30&lt;3,"poor",IF(G30&lt;=4.5,"average",IF(G30&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42787,7 +42847,7 @@
         <v>2499</v>
       </c>
       <c r="D31" s="4">
-        <f>C31-B31</f>
+        <f t="shared" si="0"/>
         <v>741</v>
       </c>
       <c r="E31" s="1">
@@ -42800,11 +42860,11 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H31" t="str">
-        <f>IF(G31&lt;3,"poor",IF(G31&lt;=4.5,"average",IF(G31&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42819,7 +42879,7 @@
         <v>999</v>
       </c>
       <c r="D32" s="4">
-        <f>C32-B32</f>
+        <f t="shared" si="0"/>
         <v>472</v>
       </c>
       <c r="E32" s="1">
@@ -42832,11 +42892,11 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H32" t="str">
-        <f>IF(G32&lt;3,"poor",IF(G32&lt;=4.5,"average",IF(G32&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42851,7 +42911,7 @@
         <v>999</v>
       </c>
       <c r="D33" s="4">
-        <f>C33-B33</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="E33" s="1">
@@ -42864,11 +42924,11 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H33" t="str">
-        <f>IF(G33&lt;3,"poor",IF(G33&lt;=4.5,"average",IF(G33&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42883,7 +42943,7 @@
         <v>1580</v>
       </c>
       <c r="D34" s="4">
-        <f>C34-B34</f>
+        <f t="shared" ref="D34:D65" si="4">C34-B34</f>
         <v>592</v>
       </c>
       <c r="E34" s="1">
@@ -42896,11 +42956,11 @@
         <v>4</v>
       </c>
       <c r="H34" t="str">
-        <f>IF(G34&lt;3,"poor",IF(G34&lt;=4.5,"average",IF(G34&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42915,7 +42975,7 @@
         <v>1350</v>
       </c>
       <c r="D35" s="4">
-        <f>C35-B35</f>
+        <f t="shared" si="4"/>
         <v>470</v>
       </c>
       <c r="E35" s="1">
@@ -42928,11 +42988,11 @@
         <v>4</v>
       </c>
       <c r="H35" t="str">
-        <f>IF(G35&lt;3,"poor",IF(G35&lt;=4.5,"average",IF(G35&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -42947,7 +43007,7 @@
         <v>647</v>
       </c>
       <c r="D36" s="4">
-        <f>C36-B36</f>
+        <f t="shared" si="4"/>
         <v>317</v>
       </c>
       <c r="E36" s="1">
@@ -42960,11 +43020,11 @@
         <v>4</v>
       </c>
       <c r="H36" t="str">
-        <f>IF(G36&lt;3,"poor",IF(G36&lt;=4.5,"average",IF(G36&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -42979,7 +43039,7 @@
         <v>3290</v>
       </c>
       <c r="D37" s="4">
-        <f>C37-B37</f>
+        <f t="shared" si="4"/>
         <v>291</v>
       </c>
       <c r="E37" s="1">
@@ -42992,11 +43052,11 @@
         <v>4</v>
       </c>
       <c r="H37" t="str">
-        <f>IF(G37&lt;3,"poor",IF(G37&lt;=4.5,"average",IF(G37&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -43011,7 +43071,7 @@
         <v>2929</v>
       </c>
       <c r="D38" s="4">
-        <f>C38-B38</f>
+        <f t="shared" si="4"/>
         <v>1329</v>
       </c>
       <c r="E38" s="1">
@@ -43024,11 +43084,11 @@
         <v>3.8</v>
       </c>
       <c r="H38" t="str">
-        <f>IF(G38&lt;3,"poor",IF(G38&lt;=4.5,"average",IF(G38&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I38" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43043,7 +43103,7 @@
         <v>1990</v>
       </c>
       <c r="D39" s="4">
-        <f>C39-B39</f>
+        <f t="shared" si="4"/>
         <v>640</v>
       </c>
       <c r="E39" s="1">
@@ -43056,11 +43116,11 @@
         <v>3.8</v>
       </c>
       <c r="H39" t="str">
-        <f>IF(G39&lt;3,"poor",IF(G39&lt;=4.5,"average",IF(G39&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I39" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -43075,7 +43135,7 @@
         <v>3520</v>
       </c>
       <c r="D40" s="4">
-        <f>C40-B40</f>
+        <f t="shared" si="4"/>
         <v>640</v>
       </c>
       <c r="E40" s="1">
@@ -43088,11 +43148,11 @@
         <v>3.8</v>
       </c>
       <c r="H40" t="str">
-        <f>IF(G40&lt;3,"poor",IF(G40&lt;=4.5,"average",IF(G40&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I40" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -43107,7 +43167,7 @@
         <v>80</v>
       </c>
       <c r="D41" s="4">
-        <f>C41-B41</f>
+        <f t="shared" si="4"/>
         <v>42</v>
       </c>
       <c r="E41" s="1">
@@ -43120,11 +43180,11 @@
         <v>3.3</v>
       </c>
       <c r="H41" t="str">
-        <f>IF(G41&lt;3,"poor",IF(G41&lt;=4.5,"average",IF(G41&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I41" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43139,7 +43199,7 @@
         <v>6143</v>
       </c>
       <c r="D42" s="4">
-        <f>C42-B42</f>
+        <f t="shared" si="4"/>
         <v>2393</v>
       </c>
       <c r="E42" s="1">
@@ -43152,11 +43212,11 @@
         <v>3</v>
       </c>
       <c r="H42" t="str">
-        <f>IF(G42&lt;3,"poor",IF(G42&lt;=4.5,"average",IF(G42&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I42" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -43171,7 +43231,7 @@
         <v>2199</v>
       </c>
       <c r="D43" s="4">
-        <f>C43-B43</f>
+        <f t="shared" si="4"/>
         <v>1010</v>
       </c>
       <c r="E43" s="1">
@@ -43184,11 +43244,11 @@
         <v>3</v>
       </c>
       <c r="H43" t="str">
-        <f>IF(G43&lt;3,"poor",IF(G43&lt;=4.5,"average",IF(G43&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I43" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43203,7 +43263,7 @@
         <v>3240</v>
       </c>
       <c r="D44" s="4">
-        <f>C44-B44</f>
+        <f t="shared" si="4"/>
         <v>940</v>
       </c>
       <c r="E44" s="1">
@@ -43216,11 +43276,11 @@
         <v>3</v>
       </c>
       <c r="H44" t="str">
-        <f>IF(G44&lt;3,"poor",IF(G44&lt;=4.5,"average",IF(G44&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I44" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -43235,7 +43295,7 @@
         <v>986</v>
       </c>
       <c r="D45" s="4">
-        <f>C45-B45</f>
+        <f t="shared" si="4"/>
         <v>528</v>
       </c>
       <c r="E45" s="1">
@@ -43248,11 +43308,11 @@
         <v>3</v>
       </c>
       <c r="H45" t="str">
-        <f>IF(G45&lt;3,"poor",IF(G45&lt;=4.5,"average",IF(G45&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I45" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43267,7 +43327,7 @@
         <v>899</v>
       </c>
       <c r="D46" s="4">
-        <f>C46-B46</f>
+        <f t="shared" si="4"/>
         <v>390</v>
       </c>
       <c r="E46" s="1">
@@ -43280,11 +43340,11 @@
         <v>3</v>
       </c>
       <c r="H46" t="str">
-        <f>IF(G46&lt;3,"poor",IF(G46&lt;=4.5,"average",IF(G46&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>average</v>
       </c>
       <c r="I46" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43299,7 +43359,7 @@
         <v>1555</v>
       </c>
       <c r="D47" s="4">
-        <f>C47-B47</f>
+        <f t="shared" si="4"/>
         <v>335</v>
       </c>
       <c r="E47" s="1">
@@ -43312,11 +43372,11 @@
         <v>2.9</v>
       </c>
       <c r="H47" t="str">
-        <f>IF(G47&lt;3,"poor",IF(G47&lt;=4.5,"average",IF(G47&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I47" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -43331,7 +43391,7 @@
         <v>873</v>
       </c>
       <c r="D48" s="4">
-        <f>C48-B48</f>
+        <f t="shared" si="4"/>
         <v>428</v>
       </c>
       <c r="E48" s="1">
@@ -43344,11 +43404,11 @@
         <v>2.8</v>
       </c>
       <c r="H48" t="str">
-        <f>IF(G48&lt;3,"poor",IF(G48&lt;=4.5,"average",IF(G48&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I48" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43363,7 +43423,7 @@
         <v>680</v>
       </c>
       <c r="D49" s="4">
-        <f>C49-B49</f>
+        <f t="shared" si="4"/>
         <v>355</v>
       </c>
       <c r="E49" s="1">
@@ -43376,11 +43436,11 @@
         <v>2.7</v>
       </c>
       <c r="H49" t="str">
-        <f>IF(G49&lt;3,"poor",IF(G49&lt;=4.5,"average",IF(G49&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I49" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43395,7 +43455,7 @@
         <v>700</v>
       </c>
       <c r="D50" s="4">
-        <f>C50-B50</f>
+        <f t="shared" si="4"/>
         <v>318</v>
       </c>
       <c r="E50" s="1">
@@ -43408,11 +43468,11 @@
         <v>2.6</v>
       </c>
       <c r="H50" t="str">
-        <f>IF(G50&lt;3,"poor",IF(G50&lt;=4.5,"average",IF(G50&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43427,7 +43487,7 @@
         <v>2500</v>
       </c>
       <c r="D51" s="4">
-        <f>C51-B51</f>
+        <f t="shared" si="4"/>
         <v>330</v>
       </c>
       <c r="E51" s="1">
@@ -43440,11 +43500,11 @@
         <v>2.5</v>
       </c>
       <c r="H51" t="str">
-        <f>IF(G51&lt;3,"poor",IF(G51&lt;=4.5,"average",IF(G51&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I51" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -43459,7 +43519,7 @@
         <v>2000</v>
       </c>
       <c r="D52" s="4">
-        <f>C52-B52</f>
+        <f t="shared" si="4"/>
         <v>1000</v>
       </c>
       <c r="E52" s="1">
@@ -43472,11 +43532,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="H52" t="str">
-        <f>IF(G52&lt;3,"poor",IF(G52&lt;=4.5,"average",IF(G52&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43491,7 +43551,7 @@
         <v>602</v>
       </c>
       <c r="D53" s="4">
-        <f>C53-B53</f>
+        <f t="shared" si="4"/>
         <v>257</v>
       </c>
       <c r="E53" s="1">
@@ -43504,11 +43564,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="H53" t="str">
-        <f>IF(G53&lt;3,"poor",IF(G53&lt;=4.5,"average",IF(G53&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43523,7 +43583,7 @@
         <v>1814</v>
       </c>
       <c r="D54" s="4">
-        <f>C54-B54</f>
+        <f t="shared" si="4"/>
         <v>846</v>
       </c>
       <c r="E54" s="1">
@@ -43536,11 +43596,11 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="H54" t="str">
-        <f>IF(G54&lt;3,"poor",IF(G54&lt;=4.5,"average",IF(G54&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43555,7 +43615,7 @@
         <v>1814</v>
       </c>
       <c r="D55" s="4">
-        <f>C55-B55</f>
+        <f t="shared" si="4"/>
         <v>824</v>
       </c>
       <c r="E55" s="1">
@@ -43568,11 +43628,11 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="H55" t="str">
-        <f>IF(G55&lt;3,"poor",IF(G55&lt;=4.5,"average",IF(G55&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="3"/>
         <v>poor</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43587,7 +43647,7 @@
         <v>4700</v>
       </c>
       <c r="D56" s="4">
-        <f>C56-B56</f>
+        <f t="shared" si="4"/>
         <v>2585</v>
       </c>
       <c r="E56" s="1">
@@ -43600,11 +43660,11 @@
         <v>2.1</v>
       </c>
       <c r="H56" t="str">
-        <f>IF(G56&lt;3,"poor",IF(G56&lt;=4.5,"average",IF(G56&gt;=4.5,"excellent","")))</f>
+        <f t="shared" ref="H56:H87" si="5">IF(G56&lt;3,"poor",IF(G56&lt;=4.5,"average",IF(G56&gt;=4.5,"excellent","")))</f>
         <v>poor</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43619,7 +43679,7 @@
         <v>2988</v>
       </c>
       <c r="D57" s="4">
-        <f>C57-B57</f>
+        <f t="shared" si="4"/>
         <v>1418</v>
       </c>
       <c r="E57" s="1">
@@ -43632,11 +43692,11 @@
         <v>2.1</v>
       </c>
       <c r="H57" t="str">
-        <f>IF(G57&lt;3,"poor",IF(G57&lt;=4.5,"average",IF(G57&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43651,7 +43711,7 @@
         <v>900</v>
       </c>
       <c r="D58" s="4">
-        <f>C58-B58</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="E58" s="1">
@@ -43664,11 +43724,11 @@
         <v>2</v>
       </c>
       <c r="H58" t="str">
-        <f>IF(G58&lt;3,"poor",IF(G58&lt;=4.5,"average",IF(G58&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43683,18 +43743,18 @@
         <v>4080</v>
       </c>
       <c r="D59" s="4">
-        <f>C59-B59</f>
+        <f t="shared" si="4"/>
         <v>1880</v>
       </c>
       <c r="E59" s="1">
         <v>0.46</v>
       </c>
       <c r="H59" t="str">
-        <f>IF(G59&lt;3,"poor",IF(G59&lt;=4.5,"average",IF(G59&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43709,18 +43769,18 @@
         <v>4471</v>
       </c>
       <c r="D60" s="4">
-        <f>C60-B60</f>
+        <f t="shared" si="4"/>
         <v>1721</v>
       </c>
       <c r="E60" s="1">
         <v>0.38</v>
       </c>
       <c r="H60" t="str">
-        <f>IF(G60&lt;3,"poor",IF(G60&lt;=4.5,"average",IF(G60&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -43735,18 +43795,18 @@
         <v>3220</v>
       </c>
       <c r="D61" s="4">
-        <f>C61-B61</f>
+        <f t="shared" si="4"/>
         <v>1360</v>
       </c>
       <c r="E61" s="1">
         <v>0.42</v>
       </c>
       <c r="H61" t="str">
-        <f>IF(G61&lt;3,"poor",IF(G61&lt;=4.5,"average",IF(G61&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I61" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43761,18 +43821,18 @@
         <v>2500</v>
       </c>
       <c r="D62" s="4">
-        <f>C62-B62</f>
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
       <c r="E62" s="1">
         <v>0.48</v>
       </c>
       <c r="H62" t="str">
-        <f>IF(G62&lt;3,"poor",IF(G62&lt;=4.5,"average",IF(G62&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I62" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43787,18 +43847,18 @@
         <v>2400</v>
       </c>
       <c r="D63" s="4">
-        <f>C63-B63</f>
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
       <c r="E63" s="1">
         <v>0.5</v>
       </c>
       <c r="H63" t="str">
-        <f>IF(G63&lt;3,"poor",IF(G63&lt;=4.5,"average",IF(G63&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43813,18 +43873,18 @@
         <v>3810</v>
       </c>
       <c r="D64" s="4">
-        <f>C64-B64</f>
+        <f t="shared" si="4"/>
         <v>1011</v>
       </c>
       <c r="E64" s="1">
         <v>0.27</v>
       </c>
       <c r="H64" t="str">
-        <f>IF(G64&lt;3,"poor",IF(G64&lt;=4.5,"average",IF(G64&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I64" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -43839,18 +43899,18 @@
         <v>2000</v>
       </c>
       <c r="D65" s="4">
-        <f>C65-B65</f>
+        <f t="shared" si="4"/>
         <v>1001</v>
       </c>
       <c r="E65" s="1">
         <v>0.5</v>
       </c>
       <c r="H65" t="str">
-        <f>IF(G65&lt;3,"poor",IF(G65&lt;=4.5,"average",IF(G65&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I65" t="str">
-        <f t="shared" ref="I65:I115" si="1">IF(E65&lt;20%,"lowdiscount",IF(E65&lt;41%,"medium discount",IF(E65&gt;=41%,"high discount","cant rate")))</f>
+        <f t="shared" ref="I65:I115" si="6">IF(E65&lt;20%,"lowdiscount",IF(E65&lt;41%,"medium discount",IF(E65&gt;=41%,"high discount","cant rate")))</f>
         <v>high discount</v>
       </c>
     </row>
@@ -43865,18 +43925,18 @@
         <v>2420</v>
       </c>
       <c r="D66" s="4">
-        <f>C66-B66</f>
+        <f t="shared" ref="D66:D97" si="7">C66-B66</f>
         <v>1000</v>
       </c>
       <c r="E66" s="1">
         <v>0.41</v>
       </c>
       <c r="H66" t="str">
-        <f>IF(G66&lt;3,"poor",IF(G66&lt;=4.5,"average",IF(G66&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I66" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43891,18 +43951,18 @@
         <v>1700</v>
       </c>
       <c r="D67" s="4">
-        <f>C67-B67</f>
+        <f t="shared" si="7"/>
         <v>850</v>
       </c>
       <c r="E67" s="1">
         <v>0.5</v>
       </c>
       <c r="H67" t="str">
-        <f>IF(G67&lt;3,"poor",IF(G67&lt;=4.5,"average",IF(G67&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43917,18 +43977,18 @@
         <v>2290</v>
       </c>
       <c r="D68" s="4">
-        <f>C68-B68</f>
+        <f t="shared" si="7"/>
         <v>830</v>
       </c>
       <c r="E68" s="1">
         <v>0.36</v>
       </c>
       <c r="H68" t="str">
-        <f>IF(G68&lt;3,"poor",IF(G68&lt;=4.5,"average",IF(G68&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -43943,18 +44003,18 @@
         <v>1699</v>
       </c>
       <c r="D69" s="4">
-        <f>C69-B69</f>
+        <f t="shared" si="7"/>
         <v>800</v>
       </c>
       <c r="E69" s="1">
         <v>0.47</v>
       </c>
       <c r="H69" t="str">
-        <f>IF(G69&lt;3,"poor",IF(G69&lt;=4.5,"average",IF(G69&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43969,18 +44029,18 @@
         <v>1699</v>
       </c>
       <c r="D70" s="4">
-        <f>C70-B70</f>
+        <f t="shared" si="7"/>
         <v>800</v>
       </c>
       <c r="E70" s="1">
         <v>0.47</v>
       </c>
       <c r="H70" t="str">
-        <f>IF(G70&lt;3,"poor",IF(G70&lt;=4.5,"average",IF(G70&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -43995,18 +44055,18 @@
         <v>1874</v>
       </c>
       <c r="D71" s="4">
-        <f>C71-B71</f>
+        <f t="shared" si="7"/>
         <v>794</v>
       </c>
       <c r="E71" s="1">
         <v>0.42</v>
       </c>
       <c r="H71" t="str">
-        <f>IF(G71&lt;3,"poor",IF(G71&lt;=4.5,"average",IF(G71&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I71" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44021,18 +44081,18 @@
         <v>1567</v>
       </c>
       <c r="D72" s="4">
-        <f>C72-B72</f>
+        <f t="shared" si="7"/>
         <v>768</v>
       </c>
       <c r="E72" s="1">
         <v>0.49</v>
       </c>
       <c r="H72" t="str">
-        <f>IF(G72&lt;3,"poor",IF(G72&lt;=4.5,"average",IF(G72&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44047,18 +44107,18 @@
         <v>1950</v>
       </c>
       <c r="D73" s="4">
-        <f>C73-B73</f>
+        <f t="shared" si="7"/>
         <v>750</v>
       </c>
       <c r="E73" s="1">
         <v>0.38</v>
       </c>
       <c r="H73" t="str">
-        <f>IF(G73&lt;3,"poor",IF(G73&lt;=4.5,"average",IF(G73&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I73" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -44073,18 +44133,18 @@
         <v>1485</v>
       </c>
       <c r="D74" s="4">
-        <f>C74-B74</f>
+        <f t="shared" si="7"/>
         <v>695</v>
       </c>
       <c r="E74" s="1">
         <v>0.47</v>
       </c>
       <c r="H74" t="str">
-        <f>IF(G74&lt;3,"poor",IF(G74&lt;=4.5,"average",IF(G74&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44099,18 +44159,18 @@
         <v>1316</v>
       </c>
       <c r="D75" s="4">
-        <f>C75-B75</f>
+        <f t="shared" si="7"/>
         <v>645</v>
       </c>
       <c r="E75" s="1">
         <v>0.49</v>
       </c>
       <c r="H75" t="str">
-        <f>IF(G75&lt;3,"poor",IF(G75&lt;=4.5,"average",IF(G75&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I75" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44125,18 +44185,18 @@
         <v>1343</v>
       </c>
       <c r="D76" s="4">
-        <f>C76-B76</f>
+        <f t="shared" si="7"/>
         <v>644</v>
       </c>
       <c r="E76" s="1">
         <v>0.48</v>
       </c>
       <c r="H76" t="str">
-        <f>IF(G76&lt;3,"poor",IF(G76&lt;=4.5,"average",IF(G76&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I76" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44151,18 +44211,18 @@
         <v>1288</v>
       </c>
       <c r="D77" s="4">
-        <f>C77-B77</f>
+        <f t="shared" si="7"/>
         <v>631</v>
       </c>
       <c r="E77" s="1">
         <v>0.49</v>
       </c>
       <c r="H77" t="str">
-        <f>IF(G77&lt;3,"poor",IF(G77&lt;=4.5,"average",IF(G77&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44177,18 +44237,18 @@
         <v>1810</v>
       </c>
       <c r="D78" s="4">
-        <f>C78-B78</f>
+        <f t="shared" si="7"/>
         <v>620</v>
       </c>
       <c r="E78" s="1">
         <v>0.34</v>
       </c>
       <c r="H78" t="str">
-        <f>IF(G78&lt;3,"poor",IF(G78&lt;=4.5,"average",IF(G78&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I78" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -44203,18 +44263,18 @@
         <v>1785</v>
       </c>
       <c r="D79" s="4">
-        <f>C79-B79</f>
+        <f t="shared" si="7"/>
         <v>595</v>
       </c>
       <c r="E79" s="1">
         <v>0.33</v>
       </c>
       <c r="H79" t="str">
-        <f>IF(G79&lt;3,"poor",IF(G79&lt;=4.5,"average",IF(G79&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I79" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -44229,18 +44289,18 @@
         <v>1737</v>
       </c>
       <c r="D80" s="4">
-        <f>C80-B80</f>
+        <f t="shared" si="7"/>
         <v>587</v>
       </c>
       <c r="E80" s="1">
         <v>0.34</v>
       </c>
       <c r="H80" t="str">
-        <f>IF(G80&lt;3,"poor",IF(G80&lt;=4.5,"average",IF(G80&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I80" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -44255,18 +44315,18 @@
         <v>1343</v>
       </c>
       <c r="D81" s="4">
-        <f>C81-B81</f>
+        <f t="shared" si="7"/>
         <v>544</v>
       </c>
       <c r="E81" s="1">
         <v>0.41</v>
       </c>
       <c r="H81" t="str">
-        <f>IF(G81&lt;3,"poor",IF(G81&lt;=4.5,"average",IF(G81&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I81" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44281,18 +44341,18 @@
         <v>1200</v>
       </c>
       <c r="D82" s="4">
-        <f>C82-B82</f>
+        <f t="shared" si="7"/>
         <v>510</v>
       </c>
       <c r="E82" s="1">
         <v>0.43</v>
       </c>
       <c r="H82" t="str">
-        <f>IF(G82&lt;3,"poor",IF(G82&lt;=4.5,"average",IF(G82&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I82" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44307,18 +44367,18 @@
         <v>1029</v>
       </c>
       <c r="D83" s="4">
-        <f>C83-B83</f>
+        <f t="shared" si="7"/>
         <v>504</v>
       </c>
       <c r="E83" s="1">
         <v>0.49</v>
       </c>
       <c r="H83" t="str">
-        <f>IF(G83&lt;3,"poor",IF(G83&lt;=4.5,"average",IF(G83&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I83" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44333,18 +44393,18 @@
         <v>896</v>
       </c>
       <c r="D84" s="4">
-        <f>C84-B84</f>
+        <f t="shared" si="7"/>
         <v>497</v>
       </c>
       <c r="E84" s="1">
         <v>0.55000000000000004</v>
       </c>
       <c r="H84" t="str">
-        <f>IF(G84&lt;3,"poor",IF(G84&lt;=4.5,"average",IF(G84&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44359,18 +44419,18 @@
         <v>1100</v>
       </c>
       <c r="D85" s="4">
-        <f>C85-B85</f>
+        <f t="shared" si="7"/>
         <v>470</v>
       </c>
       <c r="E85" s="1">
         <v>0.43</v>
       </c>
       <c r="H85" t="str">
-        <f>IF(G85&lt;3,"poor",IF(G85&lt;=4.5,"average",IF(G85&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I85" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44385,18 +44445,18 @@
         <v>931</v>
       </c>
       <c r="D86" s="4">
-        <f>C86-B86</f>
+        <f t="shared" si="7"/>
         <v>456</v>
       </c>
       <c r="E86" s="1">
         <v>0.49</v>
       </c>
       <c r="H86" t="str">
-        <f>IF(G86&lt;3,"poor",IF(G86&lt;=4.5,"average",IF(G86&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44411,18 +44471,18 @@
         <v>1060</v>
       </c>
       <c r="D87" s="4">
-        <f>C87-B87</f>
+        <f t="shared" si="7"/>
         <v>450</v>
       </c>
       <c r="E87" s="1">
         <v>0.42</v>
       </c>
       <c r="H87" t="str">
-        <f>IF(G87&lt;3,"poor",IF(G87&lt;=4.5,"average",IF(G87&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="5"/>
         <v>poor</v>
       </c>
       <c r="I87" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44437,18 +44497,18 @@
         <v>1060</v>
       </c>
       <c r="D88" s="4">
-        <f>C88-B88</f>
+        <f t="shared" si="7"/>
         <v>450</v>
       </c>
       <c r="E88" s="1">
         <v>0.42</v>
       </c>
       <c r="H88" t="str">
-        <f>IF(G88&lt;3,"poor",IF(G88&lt;=4.5,"average",IF(G88&gt;=4.5,"excellent","")))</f>
+        <f t="shared" ref="H88:H119" si="8">IF(G88&lt;3,"poor",IF(G88&lt;=4.5,"average",IF(G88&gt;=4.5,"excellent","")))</f>
         <v>poor</v>
       </c>
       <c r="I88" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44463,18 +44523,18 @@
         <v>1060</v>
       </c>
       <c r="D89" s="4">
-        <f>C89-B89</f>
+        <f t="shared" si="7"/>
         <v>450</v>
       </c>
       <c r="E89" s="1">
         <v>0.42</v>
       </c>
       <c r="H89" t="str">
-        <f>IF(G89&lt;3,"poor",IF(G89&lt;=4.5,"average",IF(G89&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44489,18 +44549,18 @@
         <v>900</v>
       </c>
       <c r="D90" s="4">
-        <f>C90-B90</f>
+        <f t="shared" si="7"/>
         <v>401</v>
       </c>
       <c r="E90" s="1">
         <v>0.45</v>
       </c>
       <c r="H90" t="str">
-        <f>IF(G90&lt;3,"poor",IF(G90&lt;=4.5,"average",IF(G90&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I90" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44515,18 +44575,18 @@
         <v>553</v>
       </c>
       <c r="D91" s="4">
-        <f>C91-B91</f>
+        <f t="shared" si="7"/>
         <v>354</v>
       </c>
       <c r="E91" s="1">
         <v>0.64</v>
       </c>
       <c r="H91" t="str">
-        <f>IF(G91&lt;3,"poor",IF(G91&lt;=4.5,"average",IF(G91&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I91" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44541,18 +44601,18 @@
         <v>504</v>
       </c>
       <c r="D92" s="4">
-        <f>C92-B92</f>
+        <f t="shared" si="7"/>
         <v>305</v>
       </c>
       <c r="E92" s="1">
         <v>0.61</v>
       </c>
       <c r="H92" t="str">
-        <f>IF(G92&lt;3,"poor",IF(G92&lt;=4.5,"average",IF(G92&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I92" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44567,18 +44627,18 @@
         <v>600</v>
       </c>
       <c r="D93" s="4">
-        <f>C93-B93</f>
+        <f t="shared" si="7"/>
         <v>301</v>
       </c>
       <c r="E93" s="1">
         <v>0.5</v>
       </c>
       <c r="H93" t="str">
-        <f>IF(G93&lt;3,"poor",IF(G93&lt;=4.5,"average",IF(G93&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I93" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44593,18 +44653,18 @@
         <v>537</v>
       </c>
       <c r="D94" s="4">
-        <f>C94-B94</f>
+        <f t="shared" si="7"/>
         <v>263</v>
       </c>
       <c r="E94" s="1">
         <v>0.49</v>
       </c>
       <c r="H94" t="str">
-        <f>IF(G94&lt;3,"poor",IF(G94&lt;=4.5,"average",IF(G94&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I94" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44619,18 +44679,18 @@
         <v>476</v>
       </c>
       <c r="D95" s="4">
-        <f>C95-B95</f>
+        <f t="shared" si="7"/>
         <v>238</v>
       </c>
       <c r="E95" s="1">
         <v>0.5</v>
       </c>
       <c r="H95" t="str">
-        <f>IF(G95&lt;3,"poor",IF(G95&lt;=4.5,"average",IF(G95&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I95" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44645,18 +44705,18 @@
         <v>486</v>
       </c>
       <c r="D96" s="4">
-        <f>C96-B96</f>
+        <f t="shared" si="7"/>
         <v>238</v>
       </c>
       <c r="E96" s="1">
         <v>0.49</v>
       </c>
       <c r="H96" t="str">
-        <f>IF(G96&lt;3,"poor",IF(G96&lt;=4.5,"average",IF(G96&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I96" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44671,18 +44731,18 @@
         <v>1699</v>
       </c>
       <c r="D97" s="4">
-        <f>C97-B97</f>
+        <f t="shared" si="7"/>
         <v>233</v>
       </c>
       <c r="E97" s="1">
         <v>0.14000000000000001</v>
       </c>
       <c r="H97" t="str">
-        <f>IF(G97&lt;3,"poor",IF(G97&lt;=4.5,"average",IF(G97&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I97" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -44697,18 +44757,18 @@
         <v>1699</v>
       </c>
       <c r="D98" s="4">
-        <f>C98-B98</f>
+        <f t="shared" ref="D98:D129" si="9">C98-B98</f>
         <v>231</v>
       </c>
       <c r="E98" s="1">
         <v>0.14000000000000001</v>
       </c>
       <c r="H98" t="str">
-        <f>IF(G98&lt;3,"poor",IF(G98&lt;=4.5,"average",IF(G98&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I98" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -44723,18 +44783,18 @@
         <v>450</v>
       </c>
       <c r="D99" s="4">
-        <f>C99-B99</f>
+        <f t="shared" si="9"/>
         <v>220</v>
       </c>
       <c r="E99" s="1">
         <v>0.49</v>
       </c>
       <c r="H99" t="str">
-        <f>IF(G99&lt;3,"poor",IF(G99&lt;=4.5,"average",IF(G99&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I99" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44749,18 +44809,18 @@
         <v>345</v>
       </c>
       <c r="D100" s="4">
-        <f>C100-B100</f>
+        <f t="shared" si="9"/>
         <v>169</v>
       </c>
       <c r="E100" s="1">
         <v>0.49</v>
       </c>
       <c r="H100" t="str">
-        <f>IF(G100&lt;3,"poor",IF(G100&lt;=4.5,"average",IF(G100&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I100" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44775,18 +44835,18 @@
         <v>3699</v>
       </c>
       <c r="D101" s="4">
-        <f>C101-B101</f>
+        <f t="shared" si="9"/>
         <v>153</v>
       </c>
       <c r="E101" s="1">
         <v>0.04</v>
       </c>
       <c r="H101" t="str">
-        <f>IF(G101&lt;3,"poor",IF(G101&lt;=4.5,"average",IF(G101&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I101" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -44801,18 +44861,18 @@
         <v>320</v>
       </c>
       <c r="D102" s="4">
-        <f>C102-B102</f>
+        <f t="shared" si="9"/>
         <v>151</v>
       </c>
       <c r="E102" s="1">
         <v>0.47</v>
       </c>
       <c r="H102" t="str">
-        <f>IF(G102&lt;3,"poor",IF(G102&lt;=4.5,"average",IF(G102&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I102" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44827,18 +44887,18 @@
         <v>1660</v>
       </c>
       <c r="D103" s="4">
-        <f>C103-B103</f>
+        <f t="shared" si="9"/>
         <v>134</v>
       </c>
       <c r="E103" s="1">
         <v>0.08</v>
       </c>
       <c r="H103" t="str">
-        <f>IF(G103&lt;3,"poor",IF(G103&lt;=4.5,"average",IF(G103&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I103" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -44853,18 +44913,18 @@
         <v>900</v>
       </c>
       <c r="D104" s="4">
-        <f>C104-B104</f>
+        <f t="shared" si="9"/>
         <v>101</v>
       </c>
       <c r="E104" s="1">
         <v>0.11</v>
       </c>
       <c r="H104" t="str">
-        <f>IF(G104&lt;3,"poor",IF(G104&lt;=4.5,"average",IF(G104&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I104" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -44879,18 +44939,18 @@
         <v>200</v>
       </c>
       <c r="D105" s="4">
-        <f>C105-B105</f>
+        <f t="shared" si="9"/>
         <v>95</v>
       </c>
       <c r="E105" s="1">
         <v>0.48</v>
       </c>
       <c r="H105" t="str">
-        <f>IF(G105&lt;3,"poor",IF(G105&lt;=4.5,"average",IF(G105&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I105" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>high discount</v>
       </c>
     </row>
@@ -44905,18 +44965,18 @@
         <v>384</v>
       </c>
       <c r="D106" s="4">
-        <f>C106-B106</f>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="E106" s="1">
         <v>0.22</v>
       </c>
       <c r="H106" t="str">
-        <f>IF(G106&lt;3,"poor",IF(G106&lt;=4.5,"average",IF(G106&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I106" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -44931,18 +44991,18 @@
         <v>1799</v>
       </c>
       <c r="D107" s="4">
-        <f>C107-B107</f>
+        <f t="shared" si="9"/>
         <v>67</v>
       </c>
       <c r="E107" s="1">
         <v>0.04</v>
       </c>
       <c r="H107" t="str">
-        <f>IF(G107&lt;3,"poor",IF(G107&lt;=4.5,"average",IF(G107&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I107" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -44957,18 +45017,18 @@
         <v>260</v>
       </c>
       <c r="D108" s="4">
-        <f>C108-B108</f>
+        <f t="shared" si="9"/>
         <v>62</v>
       </c>
       <c r="E108" s="1">
         <v>0.24</v>
       </c>
       <c r="H108" t="str">
-        <f>IF(G108&lt;3,"poor",IF(G108&lt;=4.5,"average",IF(G108&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I108" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>medium discount</v>
       </c>
     </row>
@@ -44983,18 +45043,18 @@
         <v>1699</v>
       </c>
       <c r="D109" s="4">
-        <f>C109-B109</f>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="E109" s="1">
         <v>0.02</v>
       </c>
       <c r="H109" t="str">
-        <f>IF(G109&lt;3,"poor",IF(G109&lt;=4.5,"average",IF(G109&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I109" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -45009,18 +45069,18 @@
         <v>1499</v>
       </c>
       <c r="D110" s="4">
-        <f>C110-B110</f>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="E110" s="1">
         <v>0.03</v>
       </c>
       <c r="H110" t="str">
-        <f>IF(G110&lt;3,"poor",IF(G110&lt;=4.5,"average",IF(G110&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I110" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -45035,18 +45095,18 @@
         <v>1699</v>
       </c>
       <c r="D111" s="4">
-        <f>C111-B111</f>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="E111" s="1">
         <v>0.02</v>
       </c>
       <c r="H111" t="str">
-        <f>IF(G111&lt;3,"poor",IF(G111&lt;=4.5,"average",IF(G111&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I111" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -45061,18 +45121,18 @@
         <v>2169</v>
       </c>
       <c r="D112" s="4">
-        <f>C112-B112</f>
+        <f t="shared" si="9"/>
         <v>37</v>
       </c>
       <c r="E112" s="1">
         <v>0.02</v>
       </c>
       <c r="H112" t="str">
-        <f>IF(G112&lt;3,"poor",IF(G112&lt;=4.5,"average",IF(G112&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I112" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -45087,18 +45147,18 @@
         <v>1499</v>
       </c>
       <c r="D113" s="4">
-        <f>C113-B113</f>
+        <f t="shared" si="9"/>
         <v>37</v>
       </c>
       <c r="E113" s="1">
         <v>0.02</v>
       </c>
       <c r="H113" t="str">
-        <f>IF(G113&lt;3,"poor",IF(G113&lt;=4.5,"average",IF(G113&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I113" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -45113,18 +45173,18 @@
         <v>1699</v>
       </c>
       <c r="D114" s="4">
-        <f>C114-B114</f>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="E114" s="1">
         <v>0.02</v>
       </c>
       <c r="H114" t="str">
-        <f>IF(G114&lt;3,"poor",IF(G114&lt;=4.5,"average",IF(G114&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I114" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -45139,18 +45199,18 @@
         <v>1799</v>
       </c>
       <c r="D115" s="4">
-        <f>C115-B115</f>
+        <f t="shared" si="9"/>
         <v>31</v>
       </c>
       <c r="E115" s="1">
         <v>0.02</v>
       </c>
       <c r="H115" t="str">
-        <f>IF(G115&lt;3,"poor",IF(G115&lt;=4.5,"average",IF(G115&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
       <c r="I115" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>lowdiscount</v>
       </c>
     </row>
@@ -45165,14 +45225,14 @@
         <v>1899</v>
       </c>
       <c r="D116" s="4">
-        <f>C116-B116</f>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="E116" s="1">
         <v>0.01</v>
       </c>
       <c r="H116" t="str">
-        <f>IF(G116&lt;3,"poor",IF(G116&lt;=4.5,"average",IF(G116&gt;=4.5,"excellent","")))</f>
+        <f t="shared" si="8"/>
         <v>poor</v>
       </c>
     </row>
@@ -45188,27 +45248,27 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B118" s="3">
-        <f>AVERAGE(B27:B48)</f>
+        <f t="shared" ref="B118:G118" si="10">AVERAGE(B27:B48)</f>
         <v>1277</v>
       </c>
       <c r="C118" s="3">
-        <f>AVERAGE(C27:C48)</f>
+        <f t="shared" si="10"/>
         <v>1945.6818181818182</v>
       </c>
       <c r="D118" s="3">
-        <f>AVERAGE(D27:D48)</f>
+        <f t="shared" si="10"/>
         <v>668.68181818181813</v>
       </c>
       <c r="E118" s="9">
-        <f>AVERAGE(E27:E48)</f>
+        <f t="shared" si="10"/>
         <v>0.37772727272727269</v>
       </c>
       <c r="F118" s="7">
-        <f>AVERAGE(F27:F48)</f>
+        <f t="shared" si="10"/>
         <v>13.045454545454545</v>
       </c>
       <c r="G118" s="5">
-        <f>AVERAGE(G27:G48)</f>
+        <f t="shared" si="10"/>
         <v>3.6727272727272724</v>
       </c>
     </row>
